--- a/medford_printery_dlya_uzi.xlsx
+++ b/medford_printery_dlya_uzi.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Принтеры для УЗИ для оснащения клиник и медицинских учреждений. В каталоге представлено 5 позиций.</t>
+          <t>Принтеры для УЗИ для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_printery_dlya_uzi.xlsx
+++ b/medford_printery_dlya_uzi.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать принтеры для УЗИ для клиники?</t>
+          <t>Какой принтер подходит для моего УЗИ-аппарата?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Печать, Скорость печати, Качество печати, Размер бумаги для печати). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Принтер подбирают по типу выхода сканера: цифровому (USB) или аналоговому видеосигналу. Цифровые модели (Sony UP-D898MD) работают по USB, гибридные (Sony UP-X898MD) поддерживают оба варианта, аналоговые серии Mitsubishi P93 — видеосигнал. Совместимость с конкретной моделью аппарата уточняют до покупки.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем цифровой принтер отличается от аналогового?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Цифровой принтер получает изображение по цифровому интерфейсу (например, USB) и проще интегрируется в современные системы. Аналоговый принимает видеосигнал со сканера. Гибридные модели вроде Sony UP-X898MD поддерживают оба типа подключения, что делает их универсальнее при работе с разным парком аппаратов.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Цветные принтеры для УЗИ бывают?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Представленные в каталоге медицинские принтеры для УЗИ выполняют чёрно-белую термопечать — это стандарт для документирования ультразвуковых снимков. Модели Sony и Mitsubishi печатают в оттенках серого с высоким качеством. Потребность в цвете определяется характером исследований и требованиями к оформлению протокола.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какая скорость печати у принтеров для УЗИ?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>У большинства моделей печать одного снимка занимает 1,9 секунды (Sony UP-D898MD, UP-X898MD, Mitsubishi P95DE и P95DW-DC), у Mitsubishi P93E — 3,9 секунды. Высокая скорость важна при большом потоке пациентов, когда каждое исследование сопровождается распечаткой изображений.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Какая бумага нужна для термопринтера?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Принтеры для УЗИ работают на специальной термобумаге; ширина бумаги у представленных моделей — 110 мм. Расходники подбирают под конкретную модель принтера. До покупки стоит убедиться, что подходящая термобумага доступна, и планировать запас, чтобы печать не прерывалась.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Где можно купить аппарат для УЗИ?</t>
+          <t>Чем Sony UP-D898MD отличается от UP-X898MD?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Sony UP-D898MD — компактный цифровой принтер формата A6 с подключением по USB, площадь изображения 320×100 мм. UP-X898MD — гибридная модель, поддерживающая цифровое и аналоговое подключение, с той же площадью изображения 320×100 мм. Выбор зависит от интерфейса вашего сканера.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какова цена УФ-принтера?</t>
+          <t>Нужно ли регистрационное удостоверение на принтер?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да. Медицинский принтер для УЗИ — медицинское изделие, его применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель у поставщика и проверьте его актуальность.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Как подключается принтер к сканеру?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Способ подключения зависит от модели: цифровые принтеры подключают по USB, аналоговые — через видеовыход сканера, гибридные поддерживают оба варианта. Перед покупкой уточняют доступные интерфейсы вашего УЗИ-аппарата, чтобы принтер корректно получал изображение для печати.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>printery_dlya_uzi</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Принтеры для УЗИ для оснащения клиник и медицинских учреждений.</t>
+          <t>Принтеры для УЗИ — медицинские термопринтеры для чёрно-белой печати изображений с ультразвуковых сканеров. В каталоге представлены модели Sony (UP-D898MD, UP-X898MD) и Mitsubishi Electric (P95DE, P95DW-DC, P93E) с высоким качеством печати и шириной бумаги 110 мм. Скорость печати составляет 1,9 секунды у большинства моделей, у P93E — 3,9 секунды. Площадь изображения варьирует от 100×75 мм до 320×100 мм в зависимости от модели. Приборы подключаются к сканеру и служат для быстрой распечатки снимков в ходе исследования.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое принтеры для УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3547,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3873,12 +3911,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип подключения сканера</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается принтеры для УЗИ: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Уточните, какой выход у вашего УЗИ-аппарата: цифровой (USB) или аналоговый видеовыход. Цифровые принтеры (Sony UP-D898MD) подключаются по USB к современным системам, аналоговые и гибридные модели работают с видеосигналом. Тип подключения — первое, что проверяют при подборе.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3918,12 +3956,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Проверьте совместимость с моделью УЗИ</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Принтер должен корректно работать с вашим сканером по интерфейсу и сигналу. Гибридная модель Sony UP-X898MD поддерживает и цифровое, и аналоговое подключение, что расширяет совместимость. Совместимость с конкретной моделью аппарата уточняют до покупки.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3963,12 +4001,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Выберите нужный формат изображения</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Печать, Скорость печати, Качество печати, Размер бумаги для печати. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Площадь изображения различается: у Sony UP-D898MD и UP-X898MD — 320×100 мм, у Mitsubishi P95DE — 100×75 мм, у P93E — до 99×133 мм в продольном режиме. Формат подбирают под то, как оформляются снимки в протоколе исследования.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4008,12 +4046,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените скорость печати</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Скорость влияет на темп приёма. У большинства моделей (Sony UP-D898MD, UP-X898MD, Mitsubishi P95DE, P95DW-DC) печать занимает 1,9 секунды, у Mitsubishi P93E — 3,9 секунды. При большом потоке пациентов быстрая печать сокращает время исследования.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4053,12 +4091,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Учтите доступность термобумаги</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Термопринтеры работают на специальной термобумаге шириной 110 мм. До покупки убедитесь, что расходники для выбранной модели доступны и есть в наличии. Отсутствие подходящей бумаги останавливает печать, поэтому запас расходников планируют заранее.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4098,12 +4136,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте документы и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Убедитесь в наличии действующего регистрационного удостоверения Росздравнадзора на принтер как медицинское изделие. Уточните доступность сервиса и запчастей для выбранной модели, чтобы при необходимости быстро восстановить работу прибора.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4153,7 +4191,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Принтеры для УЗИ подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на печать, скорость печати, качество печати, размер бумаги для печати, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Принтер для УЗИ выбирают под конкретный сканер: важно, поддерживает ли аппарат цифровое подключение по USB или только аналоговый видеовыход. Цифровые модели вроде Sony UP-D898MD удобнее интегрировать в современные системы, аналоговые серии Mitsubishi P93 надёжны и неприхотливы. Отдельно смотрю на доступность термобумаги нужной ширины — расходники должны быть в наличии, иначе простаивает и сам принтер, и приём.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4437,13 +4475,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое принтеры для УЗИ</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Принтеры для УЗИ — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>Принтер для УЗИ — медицинский термопринтер для чёрно-белой печати изображений с ультразвукового сканера. В каталоге модели Sony (UP-D898MD, UP-X898MD) и Mitsubishi Electric (P95DE, P95DW-DC, P93E) с шириной бумаги 110 мм, скоростью печати 1,9–3,9 секунды и высоким качеством печати. Площадь изображения — от 100×75 мм до 320×100 мм. При выборе учитывают тип подключения (цифровое USB или аналоговое), совместимость с моделью сканера и доступность термобумаги. Sony UP-D898MD — компактный цифровой принтер, UP-X898MD — гибридная цифро-аналоговая модель.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4480,13 +4518,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое принтер для УЗИ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Печать, Скорость печати, Качество печати, Размер бумаги для печати), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Принтер для УЗИ — медицинский термопринтер, предназначенный для быстрой распечатки изображений с ультразвуковых сканеров. Он формирует чёрно-белый снимок на специальной термобумаге непосредственно в ходе исследования, что позволяет приложить изображение к протоколу и выдать пациенту. Приборы подключаются к сканеру по цифровому или аналоговому интерфейсу в зависимости от модели.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4523,13 +4561,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Типы подключения</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По типу подключения принтеры для УЗИ делят на цифровые, аналоговые и гибридные. Цифровые (Sony UP-D898MD) подключаются по USB и проще интегрируются в современные системы. Аналоговые (серия Mitsubishi P93) принимают видеосигнал. Гибридные (Sony UP-X898MD) поддерживают оба варианта, что удобно при работе с разными моделями сканеров в клинике.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4566,13 +4604,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Характеристики печати</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Представленные модели выполняют чёрно-белую термопечать высокого качества на бумаге шириной 110 мм. Скорость печати составляет 1,9 секунды у большинства моделей и 3,9 секунды у Mitsubishi P93E. Площадь изображения варьирует от 100×75 мм (Mitsubishi P95DE) до 320×100 мм (Sony UP-D898MD и UP-X898MD), что определяет формат снимка в протоколе.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4589,6 +4627,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Расходные материалы и эксплуатация</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Термопринтеры работают на специальной термобумаге, поэтому доступность расходников нужной ширины планируют заранее — при отсутствии бумаги печать останавливается. При выборе модели учитывают совместимость с парком сканеров, тип подключения и наличие сервиса. Для клиники с большим потоком пациентов важна и скорость печати, сокращающая время исследования.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>printery_dlya_uzi</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
